--- a/docs/Orlando-Toastmasters-Clubs.xlsx
+++ b/docs/Orlando-Toastmasters-Clubs.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Weekly Schedule'!$A$1:$N$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Weekly Schedule'!$A$1:$S$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -522,6 +522,12 @@
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -595,6 +601,31 @@
           <t>Miles from downtown</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Day/time as listed</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Zoom link</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Zoom meeting ID</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Zoom passcode</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>How to get in online</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -659,6 +690,19 @@
       <c r="N2" s="8" t="n">
         <v>8.6</v>
       </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>2nd &amp; 4th Monday · 8:00am</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="6" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -719,6 +763,19 @@
       <c r="N3" s="8" t="n">
         <v>28.6</v>
       </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>Mondays · 5:45pm</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -783,6 +840,23 @@
       <c r="N4" s="8" t="n">
         <v>2</v>
       </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>Mondays · 7:00 - 8:30 pm</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>https://us02web.zoom.us/j/82042838539</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>Posted in toastmasters directory</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -847,6 +921,19 @@
       <c r="N5" s="8" t="n">
         <v>21.2</v>
       </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>Monday · 7:00 PM</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -911,6 +998,27 @@
       <c r="N6" s="15" t="n">
         <v>15.8</v>
       </c>
+      <c r="O6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tuesday · 7:30 am </t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr"/>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>335 384 428</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>625124</t>
+        </is>
+      </c>
+      <c r="S6" s="13" t="inlineStr">
+        <is>
+          <t>Posted in toastmasters directory</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -975,6 +1083,19 @@
       <c r="N7" s="15" t="n">
         <v>3.8</v>
       </c>
+      <c r="O7" s="13" t="inlineStr">
+        <is>
+          <t>Tuesday · 8:00 - 9:00 am</t>
+        </is>
+      </c>
+      <c r="P7" s="12" t="inlineStr"/>
+      <c r="Q7" s="12" t="inlineStr"/>
+      <c r="R7" s="12" t="inlineStr"/>
+      <c r="S7" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -1039,6 +1160,19 @@
       <c r="N8" s="15" t="n">
         <v>9.800000000000001</v>
       </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>Tuesdays · 7:40 am network. Start 8:00 am</t>
+        </is>
+      </c>
+      <c r="P8" s="12" t="inlineStr"/>
+      <c r="Q8" s="12" t="inlineStr"/>
+      <c r="R8" s="12" t="inlineStr"/>
+      <c r="S8" s="13" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -1099,6 +1233,19 @@
       <c r="N9" s="15" t="n">
         <v>2.6</v>
       </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>2nd &amp; 4th Tuesday of the Month · 12:00 noon - 1:00 pm</t>
+        </is>
+      </c>
+      <c r="P9" s="12" t="inlineStr"/>
+      <c r="Q9" s="12" t="inlineStr"/>
+      <c r="R9" s="12" t="inlineStr"/>
+      <c r="S9" s="13" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -1163,6 +1310,19 @@
       <c r="N10" s="15" t="n">
         <v>7.5</v>
       </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>1st and 3rd Tuesday · 12:00 - 1:00pm</t>
+        </is>
+      </c>
+      <c r="P10" s="12" t="inlineStr"/>
+      <c r="Q10" s="12" t="inlineStr"/>
+      <c r="R10" s="12" t="inlineStr"/>
+      <c r="S10" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -1227,6 +1387,19 @@
       <c r="N11" s="15" t="n">
         <v>9.800000000000001</v>
       </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>Tuesday · 12:00 pm</t>
+        </is>
+      </c>
+      <c r="P11" s="12" t="inlineStr"/>
+      <c r="Q11" s="12" t="inlineStr"/>
+      <c r="R11" s="12" t="inlineStr"/>
+      <c r="S11" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -1287,6 +1460,19 @@
       <c r="N12" s="15" t="n">
         <v>17.5</v>
       </c>
+      <c r="O12" s="13" t="inlineStr">
+        <is>
+          <t>3rd Tuesday · 12:00 PM</t>
+        </is>
+      </c>
+      <c r="P12" s="12" t="inlineStr"/>
+      <c r="Q12" s="12" t="inlineStr"/>
+      <c r="R12" s="12" t="inlineStr"/>
+      <c r="S12" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -1347,6 +1533,19 @@
       <c r="N13" s="15" t="n">
         <v>8.1</v>
       </c>
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>Tuesday · 12:05pm</t>
+        </is>
+      </c>
+      <c r="P13" s="12" t="inlineStr"/>
+      <c r="Q13" s="12" t="inlineStr"/>
+      <c r="R13" s="12" t="inlineStr"/>
+      <c r="S13" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -1415,6 +1614,19 @@
       <c r="N14" s="15" t="n">
         <v>5.9</v>
       </c>
+      <c r="O14" s="13" t="inlineStr">
+        <is>
+          <t>1st &amp; 3rd Tuesdays · 2:00 PM - 3:00 PM</t>
+        </is>
+      </c>
+      <c r="P14" s="12" t="inlineStr"/>
+      <c r="Q14" s="12" t="inlineStr"/>
+      <c r="R14" s="12" t="inlineStr"/>
+      <c r="S14" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -1479,6 +1691,19 @@
       <c r="N15" s="15" t="n">
         <v>13.1</v>
       </c>
+      <c r="O15" s="13" t="inlineStr">
+        <is>
+          <t>Every Tuesday ·  at 6:30 pm</t>
+        </is>
+      </c>
+      <c r="P15" s="12" t="inlineStr"/>
+      <c r="Q15" s="12" t="inlineStr"/>
+      <c r="R15" s="12" t="inlineStr"/>
+      <c r="S15" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -1543,6 +1768,23 @@
       <c r="N16" s="15" t="n">
         <v>12</v>
       </c>
+      <c r="O16" s="13" t="inlineStr">
+        <is>
+          <t>Tuesdays · 7:00 PM - 8:00 PM</t>
+        </is>
+      </c>
+      <c r="P16" s="12" t="inlineStr"/>
+      <c r="Q16" s="12" t="inlineStr">
+        <is>
+          <t>844 4566 7824</t>
+        </is>
+      </c>
+      <c r="R16" s="12" t="inlineStr"/>
+      <c r="S16" s="13" t="inlineStr">
+        <is>
+          <t>Passcode by email: wstm32708@gmail.com (per club website)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -1607,6 +1849,19 @@
       <c r="N17" s="15" t="n">
         <v>17.2</v>
       </c>
+      <c r="O17" s="13" t="inlineStr">
+        <is>
+          <t>Tuesdays · 7:00 PM</t>
+        </is>
+      </c>
+      <c r="P17" s="12" t="inlineStr"/>
+      <c r="Q17" s="12" t="inlineStr"/>
+      <c r="R17" s="12" t="inlineStr"/>
+      <c r="S17" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1675,6 +1930,23 @@
       <c r="N18" s="8" t="n">
         <v>14.3</v>
       </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday · 7:05 am</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>https://us06web.zoom.us/j/86374731804?pwd=Dsziu7WnaSTo4JYTGPiFF2u3ILxcSS.1</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Posted in club website</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1739,6 +2011,19 @@
       <c r="N19" s="8" t="n">
         <v>0.8</v>
       </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday · 7:30 am</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1776,7 +2061,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Spanish-language</t>
+          <t>Spanish / bilingual</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -1807,6 +2092,19 @@
       <c r="N20" s="8" t="n">
         <v>5</v>
       </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday · 10:00 am</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1871,6 +2169,19 @@
       <c r="N21" s="8" t="n">
         <v>5.1</v>
       </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday · 12 pm</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1935,6 +2246,19 @@
       <c r="N22" s="8" t="n">
         <v>9.9</v>
       </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday · 12:00 pm</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1999,6 +2323,19 @@
       <c r="N23" s="8" t="n">
         <v>15.6</v>
       </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>1st &amp; 3rd Wednesday · 12:00PM</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2063,6 +2400,19 @@
       <c r="N24" s="8" t="n">
         <v>0.5</v>
       </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday · 12:15 pm</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2123,6 +2473,19 @@
       <c r="N25" s="8" t="n">
         <v>3.2</v>
       </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>2nd &amp; 4th Wednesdays (contact for link) · 4 - 5 p.m.</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2187,6 +2550,19 @@
       <c r="N26" s="8" t="n">
         <v>8.699999999999999</v>
       </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday · 7:00 pm</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2251,6 +2627,19 @@
       <c r="N27" s="8" t="n">
         <v>12.1</v>
       </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>Wednesdays · 7:00 pm</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -2315,6 +2704,23 @@
       <c r="N28" s="15" t="n">
         <v>8.800000000000001</v>
       </c>
+      <c r="O28" s="13" t="inlineStr">
+        <is>
+          <t>Online weekly. In person - 2nd Thursday · 7:30 am</t>
+        </is>
+      </c>
+      <c r="P28" s="14" t="inlineStr">
+        <is>
+          <t>https://us02web.zoom.us/j/87411966214?pwd=TlpGamwvYkhzcWF0VDg4eEdhZXdqZz09</t>
+        </is>
+      </c>
+      <c r="Q28" s="12" t="inlineStr"/>
+      <c r="R28" s="12" t="inlineStr"/>
+      <c r="S28" s="13" t="inlineStr">
+        <is>
+          <t>Posted in toastmasters directory</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -2379,6 +2785,19 @@
       <c r="N29" s="15" t="n">
         <v>10.9</v>
       </c>
+      <c r="O29" s="13" t="inlineStr">
+        <is>
+          <t>2nd &amp; 4th Thursday - Employees Only  · 8:00 AM</t>
+        </is>
+      </c>
+      <c r="P29" s="12" t="inlineStr"/>
+      <c r="Q29" s="12" t="inlineStr"/>
+      <c r="R29" s="12" t="inlineStr"/>
+      <c r="S29" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -2439,6 +2858,19 @@
       <c r="N30" s="15" t="n">
         <v>0.1</v>
       </c>
+      <c r="O30" s="13" t="inlineStr">
+        <is>
+          <t>Thursday · 12:00 pm</t>
+        </is>
+      </c>
+      <c r="P30" s="12" t="inlineStr"/>
+      <c r="Q30" s="12" t="inlineStr"/>
+      <c r="R30" s="12" t="inlineStr"/>
+      <c r="S30" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -2507,6 +2939,19 @@
       <c r="N31" s="15" t="n">
         <v>11.2</v>
       </c>
+      <c r="O31" s="13" t="inlineStr">
+        <is>
+          <t>1st Thursday of the Month · 12:00 pm</t>
+        </is>
+      </c>
+      <c r="P31" s="12" t="inlineStr"/>
+      <c r="Q31" s="12" t="inlineStr"/>
+      <c r="R31" s="12" t="inlineStr"/>
+      <c r="S31" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
@@ -2571,6 +3016,19 @@
       <c r="N32" s="15" t="n">
         <v>19</v>
       </c>
+      <c r="O32" s="13" t="inlineStr">
+        <is>
+          <t>Thursday · 5:45 pm</t>
+        </is>
+      </c>
+      <c r="P32" s="12" t="inlineStr"/>
+      <c r="Q32" s="12" t="inlineStr"/>
+      <c r="R32" s="12" t="inlineStr"/>
+      <c r="S32" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -2635,6 +3093,19 @@
       <c r="N33" s="15" t="n">
         <v>3.1</v>
       </c>
+      <c r="O33" s="13" t="inlineStr">
+        <is>
+          <t>Thursday · 6:30 pm</t>
+        </is>
+      </c>
+      <c r="P33" s="12" t="inlineStr"/>
+      <c r="Q33" s="12" t="inlineStr"/>
+      <c r="R33" s="12" t="inlineStr"/>
+      <c r="S33" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -2699,6 +3170,27 @@
       <c r="N34" s="15" t="n">
         <v>0.1</v>
       </c>
+      <c r="O34" s="13" t="inlineStr">
+        <is>
+          <t>Every Thursday  · 7:00 pm - 8:30 pm</t>
+        </is>
+      </c>
+      <c r="P34" s="12" t="inlineStr"/>
+      <c r="Q34" s="12" t="inlineStr">
+        <is>
+          <t>853 278 5238</t>
+        </is>
+      </c>
+      <c r="R34" s="12" t="inlineStr">
+        <is>
+          <t>85917</t>
+        </is>
+      </c>
+      <c r="S34" s="13" t="inlineStr">
+        <is>
+          <t>Posted in toastmasters directory</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -2763,6 +3255,19 @@
       <c r="N35" s="15" t="n">
         <v>2</v>
       </c>
+      <c r="O35" s="13" t="inlineStr">
+        <is>
+          <t>Thursdays · 7:00 pm</t>
+        </is>
+      </c>
+      <c r="P35" s="12" t="inlineStr"/>
+      <c r="Q35" s="12" t="inlineStr"/>
+      <c r="R35" s="12" t="inlineStr"/>
+      <c r="S35" s="13" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
@@ -2827,6 +3332,19 @@
       <c r="N36" s="15" t="n">
         <v>13.1</v>
       </c>
+      <c r="O36" s="13" t="inlineStr">
+        <is>
+          <t>Thursday · 7:00 pm</t>
+        </is>
+      </c>
+      <c r="P36" s="12" t="inlineStr"/>
+      <c r="Q36" s="12" t="inlineStr"/>
+      <c r="R36" s="12" t="inlineStr"/>
+      <c r="S36" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2891,6 +3409,19 @@
       <c r="N37" s="8" t="n">
         <v>4.2</v>
       </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>Friday · 7:25 am</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr"/>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2955,6 +3486,19 @@
       <c r="N38" s="8" t="n">
         <v>0.3</v>
       </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>Friday · 7:30 am</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3019,6 +3563,19 @@
       <c r="N39" s="8" t="n">
         <v>14.7</v>
       </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>Friday · 7:30 am</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="R39" s="5" t="inlineStr"/>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3079,6 +3636,19 @@
       <c r="N40" s="8" t="n">
         <v>27.8</v>
       </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>Friday · 12:00 pm - 1:00 pm</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr"/>
+      <c r="R40" s="5" t="inlineStr"/>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
@@ -3143,6 +3713,19 @@
       <c r="N41" s="15" t="n">
         <v>17.1</v>
       </c>
+      <c r="O41" s="13" t="inlineStr">
+        <is>
+          <t>Saturdays · 9:30 AM</t>
+        </is>
+      </c>
+      <c r="P41" s="12" t="inlineStr"/>
+      <c r="Q41" s="12" t="inlineStr"/>
+      <c r="R41" s="12" t="inlineStr"/>
+      <c r="S41" s="13" t="inlineStr">
+        <is>
+          <t>In person only</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3207,11 +3790,28 @@
       <c r="N42" s="8" t="n">
         <v>13.6</v>
       </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1st &amp; 3rd Sundays each month · 3:00 pm - 4:15 pm (EST) </t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>995 0171 1830</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr"/>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>Posted in toastmasters directory</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Not scheduled yet</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="B43" s="10" t="n"/>
@@ -3261,11 +3861,20 @@
       <c r="N43" s="15" t="n">
         <v>8.300000000000001</v>
       </c>
+      <c r="O43" s="13" t="inlineStr"/>
+      <c r="P43" s="12" t="inlineStr"/>
+      <c r="Q43" s="12" t="inlineStr"/>
+      <c r="R43" s="12" t="inlineStr"/>
+      <c r="S43" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Not scheduled yet</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="B44" s="10" t="n"/>
@@ -3315,84 +3924,96 @@
       <c r="N44" s="15" t="n">
         <v>15.4</v>
       </c>
+      <c r="O44" s="13" t="inlineStr"/>
+      <c r="P44" s="12" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="inlineStr"/>
+      <c r="S44" s="13" t="inlineStr">
+        <is>
+          <t>Ask the club for the link (email in this row)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N44"/>
+  <autoFilter ref="A1:S44"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3404,7 +4025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -3441,26 +4062,33 @@
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>"How often": monthly clubs such as "2nd &amp; 4th Tuesday of month" meet only in those weeks.</t>
+          <t>Zoom columns: filled only when the club posts its link publicly (in the Toastmasters directory or on its own website). Most clubs email the link to guests instead.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>"Membership may be restricted" usually means a company or government club. Guests are often welcome, but call first.</t>
+          <t>"How often": monthly clubs such as "2nd &amp; 4th Tuesday of month" meet only in those weeks. The last column shows the day/time exactly as the club lists it.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>Contact email and phone are the ones each club publishes in the Toastmasters directory; they can go stale, so confirm before driving over.</t>
+          <t>"Membership may be restricted" usually means a company or government club. Guests are often welcome, but call first.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Contact email and phone are the ones each club publishes in the Toastmasters directory; they can go stale, so confirm before driving over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Miles = straight-line distance from downtown Orlando.</t>
         </is>
